--- a/evals/e2e_tests_comparative/bert_small/analysis_output_ref/perf_report_trace1.xlsx
+++ b/evals/e2e_tests_comparative/bert_small/analysis_output_ref/perf_report_trace1.xlsx
@@ -11,12 +11,13 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Normalization" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="diff_stats" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GEMM" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SDPA_fwd" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="diff_stats" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,6 +570,638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AV3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: op_shape</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_input</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_channels</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>param: has_bias</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>param: is_affine</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>param: is_training</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>num_kernels</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Roofline Time (µs)_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Roofline Bound_first</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_mean</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_median</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_std</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_min</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_max</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::layer_norm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(1, 141, 512)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(72192, 512, 1)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000364032</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.234375</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.07476479069970718</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07470099932966896</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.003397537390332268</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.07006725939675175</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.07910671591355599</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.09228778851995104</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.09220904604756011</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.004193835216191402</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.08648927331786543</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.09764735245579566</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>thread 6240 (python3)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.05564377358490566</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>MEMORY_BOUND</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.410656428296362</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.409452817540924</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.06410447906287296</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.322023762202863</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.492579545538792</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(39.519000000000005), 'gpu_op_uids': [2477, 2497, 2507, 2521, 2531, 2545, 2555, 2569, 2579, 2585], 'mean_duration_us': np.float64(3.9519000000000006), 'median_duration_us': np.float64(3.948), 'std_dev_duration_us': np.float64(0.17117561158062206), 'min_duration_us': np.float64(3.728), 'max_duration_us': np.float64(4.209)}]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(3.95)}]</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>[[1, 141, 512], [], [512], [512], [], []]</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>[[72192, 512, 1], [], [1], [1], [], []]</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>['', '[512]', '', '', '9.9999999999999998e-13', 'True']</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>3.951904296875</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.947998046875</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.1803733893005544</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.72802734375</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.208984375</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>39.51904296875</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(1, 141, 512)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(72192, 512, 1)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.000364032</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.234375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07476479069970718</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07470099932966896</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.003397537390332268</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.07006725939675175</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.07910671591355599</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.09228778851995104</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.09220904604756011</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.004193835216191402</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.08648927331786543</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.09764735245579566</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>thread 6240 (python3)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.05564377358490566</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>MEMORY_BOUND</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.410656428296362</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.409452817540924</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.06410447906287296</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.322023762202863</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.492579545538792</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(39.519000000000005), 'gpu_op_uids': [2477, 2497, 2507, 2521, 2531, 2545, 2555, 2569, 2579, 2585], 'mean_duration_us': np.float64(3.9519000000000006), 'median_duration_us': np.float64(3.948), 'std_dev_duration_us': np.float64(0.17117561158062206), 'min_duration_us': np.float64(3.728), 'max_duration_us': np.float64(4.209)}]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(3.95)}]</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>[[1, 141, 512], [], [512], [512], []]</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>[[72192, 512, 1], [], [1], [1], []]</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>['', '[512]', '', '', '9.9999999999999998e-13']</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>3.951904296875</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.947998046875</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.1803733893005544</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.72802734375</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.208984375</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>39.51904296875</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -715,19 +1348,19 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
         <v>2467</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: Embedding</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Embedding</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -790,19 +1423,19 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
         <v>2103</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: Embedding</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Embedding</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -865,19 +1498,19 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N4" t="n">
         <v>2469</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: Embedding</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Embedding</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -940,19 +1573,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
         <v>2107</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: Embedding</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Embedding</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1015,19 +1648,19 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="N6" t="n">
         <v>2471</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1090,19 +1723,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="N7" t="n">
         <v>2111</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1165,19 +1798,19 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
         <v>2473</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: Embedding</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Embedding</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1240,19 +1873,19 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
         <v>2115</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: Embedding</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Embedding</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1315,19 +1948,19 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N10" t="n">
         <v>2475</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1390,19 +2023,19 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N11" t="n">
         <v>2119</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertEmbeddings</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1465,19 +2098,19 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N12" t="n">
         <v>2477</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1540,19 +2173,19 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N13" t="n">
         <v>2123</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEmbeddings;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1615,19 +2248,19 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="N14" t="n">
         <v>2479</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertModel</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -1690,19 +2323,19 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="N15" t="n">
         <v>2127</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertModel</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -1765,19 +2398,19 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="N16" t="n">
         <v>2481</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertModel</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -1840,19 +2473,19 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="N17" t="n">
         <v>2131</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertModel</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -1915,19 +2548,19 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="N18" t="n">
         <v>2483</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertModel</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -1990,19 +2623,19 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="N19" t="n">
         <v>2135</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertModel</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2065,19 +2698,19 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="N20" t="n">
         <v>2485</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2140,19 +2773,19 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="N21" t="n">
         <v>2145</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2215,19 +2848,19 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="N22" t="n">
         <v>2487</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2290,19 +2923,19 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="N23" t="n">
         <v>2153</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -2365,19 +2998,19 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="N24" t="n">
         <v>2489</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2440,19 +3073,19 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="N25" t="n">
         <v>2161</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2515,19 +3148,19 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="N26" t="n">
         <v>2491</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -2590,19 +3223,19 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="N27" t="n">
         <v>2169</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -2665,19 +3298,19 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="N28" t="n">
         <v>2493</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -2740,19 +3373,19 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="N29" t="n">
         <v>2177</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -2815,19 +3448,19 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="N30" t="n">
         <v>2495</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2890,19 +3523,19 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="N31" t="n">
         <v>2181</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -2965,19 +3598,19 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="N32" t="n">
         <v>2497</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -3040,19 +3673,19 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="N33" t="n">
         <v>2185</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3115,19 +3748,19 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N34" t="n">
         <v>2499</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -3190,19 +3823,19 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="N35" t="n">
         <v>2193</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -3265,19 +3898,19 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="N36" t="n">
         <v>2501</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3340,19 +3973,19 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="N37" t="n">
         <v>2197</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -3415,19 +4048,19 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="N38" t="n">
         <v>2503</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q38" t="n">
@@ -3490,19 +4123,19 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="N39" t="n">
         <v>2209</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -3565,19 +4198,19 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="N40" t="n">
         <v>2505</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -3640,19 +4273,19 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="N41" t="n">
         <v>2213</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -3715,19 +4348,19 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="N42" t="n">
         <v>2507</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3790,19 +4423,19 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="N43" t="n">
         <v>2217</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -3865,19 +4498,19 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="N44" t="n">
         <v>2509</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -3940,19 +4573,19 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="N45" t="n">
         <v>2225</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -4015,19 +4648,19 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>143</v>
+        <v>241</v>
       </c>
       <c r="N46" t="n">
         <v>2511</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -4090,19 +4723,19 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>143</v>
+        <v>241</v>
       </c>
       <c r="N47" t="n">
         <v>2233</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -4165,19 +4798,19 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="N48" t="n">
         <v>2513</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -4240,19 +4873,19 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="N49" t="n">
         <v>2241</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -4315,19 +4948,19 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="N50" t="n">
         <v>2515</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -4390,19 +5023,19 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="N51" t="n">
         <v>2249</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -4465,19 +5098,19 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="N52" t="n">
         <v>2517</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -4540,19 +5173,19 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="N53" t="n">
         <v>2257</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -4615,19 +5248,19 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>174</v>
+        <v>277</v>
       </c>
       <c r="N54" t="n">
         <v>2519</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -4690,19 +5323,19 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>174</v>
+        <v>277</v>
       </c>
       <c r="N55" t="n">
         <v>2261</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -4765,19 +5398,19 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>180</v>
+        <v>288</v>
       </c>
       <c r="N56" t="n">
         <v>2521</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4840,19 +5473,19 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>180</v>
+        <v>288</v>
       </c>
       <c r="N57" t="n">
         <v>2265</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -4915,19 +5548,19 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="N58" t="n">
         <v>2523</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -4990,19 +5623,19 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="N59" t="n">
         <v>2273</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -5065,19 +5698,19 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="N60" t="n">
         <v>2525</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -5140,19 +5773,19 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="N61" t="n">
         <v>2277</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -5215,19 +5848,19 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="N62" t="n">
         <v>2527</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -5290,19 +5923,19 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="N63" t="n">
         <v>2289</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -5365,19 +5998,19 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>203</v>
+        <v>330</v>
       </c>
       <c r="N64" t="n">
         <v>2529</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -5440,19 +6073,19 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>203</v>
+        <v>330</v>
       </c>
       <c r="N65" t="n">
         <v>2293</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q65" t="n">
@@ -5515,19 +6148,19 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>209</v>
+        <v>341</v>
       </c>
       <c r="N66" t="n">
         <v>2531</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -5590,19 +6223,19 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>209</v>
+        <v>341</v>
       </c>
       <c r="N67" t="n">
         <v>2297</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -5665,19 +6298,19 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>215</v>
+        <v>360</v>
       </c>
       <c r="N68" t="n">
         <v>2533</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -5740,19 +6373,19 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>215</v>
+        <v>360</v>
       </c>
       <c r="N69" t="n">
         <v>2305</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q69" t="n">
@@ -5815,19 +6448,19 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>223</v>
+        <v>370</v>
       </c>
       <c r="N70" t="n">
         <v>2535</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -5890,19 +6523,19 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>223</v>
+        <v>370</v>
       </c>
       <c r="N71" t="n">
         <v>2313</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -5965,19 +6598,19 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>231</v>
+        <v>380</v>
       </c>
       <c r="N72" t="n">
         <v>2537</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -6040,19 +6673,19 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>231</v>
+        <v>380</v>
       </c>
       <c r="N73" t="n">
         <v>2321</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -6115,19 +6748,19 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>240</v>
+        <v>388</v>
       </c>
       <c r="N74" t="n">
         <v>2539</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q74" t="n">
@@ -6190,19 +6823,19 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>240</v>
+        <v>388</v>
       </c>
       <c r="N75" t="n">
         <v>2329</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -6265,19 +6898,19 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>248</v>
+        <v>401</v>
       </c>
       <c r="N76" t="n">
         <v>2541</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -6340,19 +6973,19 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>248</v>
+        <v>401</v>
       </c>
       <c r="N77" t="n">
         <v>2337</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -6415,19 +7048,19 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>254</v>
+        <v>406</v>
       </c>
       <c r="N78" t="n">
         <v>2543</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -6490,19 +7123,19 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>254</v>
+        <v>406</v>
       </c>
       <c r="N79" t="n">
         <v>2341</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -6565,19 +7198,19 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>260</v>
+        <v>417</v>
       </c>
       <c r="N80" t="n">
         <v>2545</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -6640,19 +7273,19 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>260</v>
+        <v>417</v>
       </c>
       <c r="N81" t="n">
         <v>2345</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -6715,19 +7348,19 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>266</v>
+        <v>432</v>
       </c>
       <c r="N82" t="n">
         <v>2547</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -6790,19 +7423,19 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>266</v>
+        <v>432</v>
       </c>
       <c r="N83" t="n">
         <v>2353</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -6865,19 +7498,19 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>271</v>
+        <v>441</v>
       </c>
       <c r="N84" t="n">
         <v>2549</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q84" t="n">
@@ -6940,19 +7573,19 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>271</v>
+        <v>441</v>
       </c>
       <c r="N85" t="n">
         <v>2357</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -7015,19 +7648,19 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>277</v>
+        <v>454</v>
       </c>
       <c r="N86" t="n">
         <v>2551</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q86" t="n">
@@ -7090,19 +7723,19 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>277</v>
+        <v>454</v>
       </c>
       <c r="N87" t="n">
         <v>2369</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q87" t="n">
@@ -7165,19 +7798,19 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>283</v>
+        <v>459</v>
       </c>
       <c r="N88" t="n">
         <v>2553</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q88" t="n">
@@ -7240,19 +7873,19 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>283</v>
+        <v>459</v>
       </c>
       <c r="N89" t="n">
         <v>2373</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q89" t="n">
@@ -7315,19 +7948,19 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>289</v>
+        <v>470</v>
       </c>
       <c r="N90" t="n">
         <v>2555</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q90" t="n">
@@ -7390,19 +8023,19 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>289</v>
+        <v>470</v>
       </c>
       <c r="N91" t="n">
         <v>2377</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -7465,19 +8098,19 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>295</v>
+        <v>489</v>
       </c>
       <c r="N92" t="n">
         <v>2557</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q92" t="n">
@@ -7540,19 +8173,19 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>295</v>
+        <v>489</v>
       </c>
       <c r="N93" t="n">
         <v>2385</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -7615,19 +8248,19 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>303</v>
+        <v>499</v>
       </c>
       <c r="N94" t="n">
         <v>2559</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -7690,19 +8323,19 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>303</v>
+        <v>499</v>
       </c>
       <c r="N95" t="n">
         <v>2393</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -7765,19 +8398,19 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>311</v>
+        <v>509</v>
       </c>
       <c r="N96" t="n">
         <v>2561</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -7840,19 +8473,19 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>311</v>
+        <v>509</v>
       </c>
       <c r="N97" t="n">
         <v>2401</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -7915,19 +8548,19 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>320</v>
+        <v>517</v>
       </c>
       <c r="N98" t="n">
         <v>2563</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -7990,19 +8623,19 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>320</v>
+        <v>517</v>
       </c>
       <c r="N99" t="n">
         <v>2409</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSdpaSelfAttention</t>
         </is>
       </c>
       <c r="Q99" t="n">
@@ -8065,19 +8698,19 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>328</v>
+        <v>530</v>
       </c>
       <c r="N100" t="n">
         <v>2565</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -8140,19 +8773,19 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>328</v>
+        <v>530</v>
       </c>
       <c r="N101" t="n">
         <v>2417</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -8215,19 +8848,19 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>334</v>
+        <v>535</v>
       </c>
       <c r="N102" t="n">
         <v>2567</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -8290,19 +8923,19 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>334</v>
+        <v>535</v>
       </c>
       <c r="N103" t="n">
         <v>2421</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertSelfOutput</t>
         </is>
       </c>
       <c r="Q103" t="n">
@@ -8365,19 +8998,19 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>340</v>
+        <v>546</v>
       </c>
       <c r="N104" t="n">
         <v>2569</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -8440,19 +9073,19 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>340</v>
+        <v>546</v>
       </c>
       <c r="N105" t="n">
         <v>2425</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertAttention;nn.Module: BertSelfOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -8515,19 +9148,19 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>346</v>
+        <v>561</v>
       </c>
       <c r="N106" t="n">
         <v>2571</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -8590,19 +9223,19 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>346</v>
+        <v>561</v>
       </c>
       <c r="N107" t="n">
         <v>2433</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -8665,19 +9298,19 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>351</v>
+        <v>570</v>
       </c>
       <c r="N108" t="n">
         <v>2573</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -8740,19 +9373,19 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>351</v>
+        <v>570</v>
       </c>
       <c r="N109" t="n">
         <v>2437</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertIntermediate;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -8815,19 +9448,19 @@
         </is>
       </c>
       <c r="M110" t="n">
-        <v>357</v>
+        <v>583</v>
       </c>
       <c r="N110" t="n">
         <v>2575</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -8890,19 +9523,19 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>357</v>
+        <v>583</v>
       </c>
       <c r="N111" t="n">
         <v>2449</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -8965,19 +9598,19 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>363</v>
+        <v>588</v>
       </c>
       <c r="N112" t="n">
         <v>2577</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q112" t="n">
@@ -9040,19 +9673,19 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>363</v>
+        <v>588</v>
       </c>
       <c r="N113" t="n">
         <v>2453</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertOutput</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -9115,19 +9748,19 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>369</v>
+        <v>599</v>
       </c>
       <c r="N114" t="n">
         <v>2579</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -9190,19 +9823,19 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>369</v>
+        <v>599</v>
       </c>
       <c r="N115" t="n">
         <v>2457</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertModel;nn.Module: BertEncoder;nn.Module: BertLayer;nn.Module: BertOutput;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q115" t="n">
@@ -9265,19 +9898,19 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>375</v>
+        <v>618</v>
       </c>
       <c r="N116" t="n">
         <v>2581</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: BertPredictionHeadTransform;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -9340,19 +9973,19 @@
         </is>
       </c>
       <c r="M117" t="n">
-        <v>375</v>
+        <v>618</v>
       </c>
       <c r="N117" t="n">
         <v>2465</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: BertPredictionHeadTransform;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q117" t="n">
@@ -9415,19 +10048,19 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>380</v>
+        <v>627</v>
       </c>
       <c r="N118" t="n">
         <v>2583</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: BertPredictionHeadTransform;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -9490,19 +10123,19 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>380</v>
+        <v>627</v>
       </c>
       <c r="N119" t="n">
         <v>2469</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: BertPredictionHeadTransform;nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: GELUActivation</t>
         </is>
       </c>
       <c r="Q119" t="n">
@@ -9565,19 +10198,19 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>386</v>
+        <v>638</v>
       </c>
       <c r="N120" t="n">
         <v>2585</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: BertPredictionHeadTransform;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q120" t="n">
@@ -9640,19 +10273,19 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>386</v>
+        <v>638</v>
       </c>
       <c r="N121" t="n">
         <v>2473</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: BertPredictionHeadTransform;nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: LayerNorm</t>
         </is>
       </c>
       <c r="Q121" t="n">
@@ -9715,19 +10348,19 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>392</v>
+        <v>648</v>
       </c>
       <c r="N122" t="n">
         <v>2587</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q122" t="n">
@@ -9790,19 +10423,19 @@
         </is>
       </c>
       <c r="M123" t="n">
-        <v>392</v>
+        <v>648</v>
       </c>
       <c r="N123" t="n">
         <v>2481</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: BertLMHeadModel;nn.Module: BertOnlyMLMHead;nn.Module: BertLMPredictionHead;nn.Module: Linear</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>nn.Module: Linear</t>
         </is>
       </c>
       <c r="Q123" t="n">
@@ -12195,15 +12828,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>call_stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_scaled_dot_product_flash_attention</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SDPA_fwd</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aten::_scaled_dot_product_flash_attention =&gt; aten::_scaled_dot_product_flash_attention =&gt; aten::scaled_dot_product_attention =&gt; transformers/models/bert/modeling_bert.py(364): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertSdpaSelfAttention =&gt; transformers/models/bert/modeling_bert.py(505): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertAttention =&gt; transformers/models/bert/modeling_bert.py(573): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLayer =&gt; transformers/models/bert/modeling_bert.py(651): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEncoder =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Linear =&gt; transformers/models/bert/modeling_bert.py(364): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertSdpaSelfAttention =&gt; transformers/models/bert/modeling_bert.py(505): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertAttention =&gt; transformers/models/bert/modeling_bert.py(573): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLayer =&gt; transformers/models/bert/modeling_bert.py(651): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEncoder =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::layer_norm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>aten::layer_norm =&gt; aten::layer_norm =&gt; torch/nn/functional.py(2889): layer_norm =&gt; torch/nn/modules/normalization.py(216): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: LayerNorm =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEmbeddings =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Linear =&gt; transformers/models/bert/modeling_bert.py(538): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertIntermediate =&gt; transformers/models/bert/modeling_bert.py(638): feed_forward_chunk =&gt; transformers/pytorch_utils.py(186): apply_chunking_to_forward =&gt; transformers/models/bert/modeling_bert.py(573): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLayer =&gt; transformers/models/bert/modeling_bert.py(651): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEncoder =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Linear =&gt; transformers/models/bert/modeling_bert.py(551): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertOutput =&gt; transformers/models/bert/modeling_bert.py(638): feed_forward_chunk =&gt; transformers/pytorch_utils.py(186): apply_chunking_to_forward =&gt; transformers/models/bert/modeling_bert.py(573): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLayer =&gt; transformers/models/bert/modeling_bert.py(651): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEncoder =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Linear =&gt; transformers/models/bert/modeling_bert.py(786): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMPredictionHead =&gt; transformers/models/bert/modeling_bert.py(797): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertOnlyMLMHead =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>aten::add =&gt; aten::add =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEmbeddings =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>aten::gelu =&gt; aten::gelu =&gt; transformers/activations.py(77): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: GELUActivation =&gt; transformers/models/bert/modeling_bert.py(538): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertIntermediate =&gt; transformers/models/bert/modeling_bert.py(638): feed_forward_chunk =&gt; transformers/pytorch_utils.py(186): apply_chunking_to_forward =&gt; transformers/models/bert/modeling_bert.py(573): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLayer =&gt; transformers/models/bert/modeling_bert.py(651): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEncoder =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::all</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>aten::all =&gt; aten::all =&gt; transformers/modeling_attn_mask_utils.py(429): _prepared_attention_mask_for_sdpa =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>aten::eq =&gt; aten::eq =&gt; transformers/modeling_attn_mask_utils.py(429): _prepared_attention_mask_for_sdpa =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>aten::index_select =&gt; aten::index_select =&gt; aten::embedding =&gt; torch/nn/functional.py(2437): embedding =&gt; torch/nn/modules/sparse.py(189): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Embedding =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEmbeddings =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>aten::index_select =&gt; aten::index_select =&gt; aten::embedding =&gt; torch/nn/functional.py(2437): embedding =&gt; torch/nn/modules/sparse.py(189): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Embedding =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEmbeddings =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>aten::gelu =&gt; aten::gelu =&gt; transformers/activations.py(77): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: GELUActivation =&gt; transformers/models/bert/modeling_bert.py(762): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertPredictionHeadTransform =&gt; transformers/models/bert/modeling_bert.py(786): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMPredictionHead =&gt; transformers/models/bert/modeling_bert.py(797): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertOnlyMLMHead =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>aten::index_select =&gt; aten::index_select =&gt; aten::embedding =&gt; torch/nn/functional.py(2437): embedding =&gt; torch/nn/modules/sparse.py(189): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: Embedding =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEmbeddings =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>aten::add_ =&gt; aten::add_ =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertEmbeddings =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::_local_scalar_dense</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>aten::_local_scalar_dense =&gt; aten::_local_scalar_dense =&gt; aten::item =&gt; aten::is_nonzero =&gt; transformers/modeling_attn_mask_utils.py(429): _prepared_attention_mask_for_sdpa =&gt; transformers/models/bert/modeling_bert.py(1001): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertModel =&gt; transformers/models/bert/modeling_bert.py(1306): forward =&gt; torch/nn/modules/module.py(1755): _call_impl =&gt; nn.Module: BertLMHeadModel =&gt; moca/library/model_hub/huggingface/model/adapters/text_base_model.py(28): run_on_input =&gt; moca/library/model_hub/entry_point.py(106): run_action =&gt; moca/shared/maybe/_decorator.py(90): wrapper =&gt; multiprocessing/process.py(108): run =&gt; multiprocessing/spawn.py(135): _main =&gt; multiprocessing/spawn.py(122): spawn_main</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BF17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
@@ -12341,7 +13330,7 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>lca_kernel_count_trace2</t>
+          <t>lca_count_trace2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -12476,10 +13465,15 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -12597,7 +13591,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>80; 160; 240; 320</t>
+          <t>130; 259; 388; 517</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -12667,7 +13661,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>[{'name': 'attn_fwd', 'stream': 0, 'gpu_op_uid': 2491, 'count': 4, 'total_duration_us': np.float64(113.656), 'gpu_op_uids': [2491, 2515, 2539, 2563], 'mean_duration_us': np.float64(28.414), 'median_duration_us': np.float64(27.3215), 'std_dev_duration_us': np.float64(2.0935189275475854), 'min_duration_us': np.float64(26.981), 'max_duration_us': np.float64(32.032)}]</t>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(113.656), 'gpu_op_uids': [2491, 2515, 2539, 2563], 'mean_duration_us': np.float64(28.414), 'median_duration_us': np.float64(27.3215), 'std_dev_duration_us': np.float64(2.0935189275475854), 'min_duration_us': np.float64(26.981), 'max_duration_us': np.float64(32.032)}]</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -12683,12 +13677,17 @@
       <c r="BC2" t="b">
         <v>1</v>
       </c>
-      <c r="BD2" t="n">
-        <v>29.08667633860792</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>aten::_scaled_dot_product_flash_attention =&gt; aten::_scaled_dot_product_flash_attention =&gt; aten::scaled_dot_product_attention =&gt; transformers/models/bert/modeling_bert.py(364): forward</t>
+        </is>
       </c>
       <c r="BE2" t="n">
         <v>29.08667633860792</v>
       </c>
+      <c r="BF2" t="n">
+        <v>29.08667633860792</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12802,7 +13801,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>55; 63; 71; 88; 135; 143; 151; 168; 215; 223; 231; 248; 295; 303; 311; 328; 375</t>
+          <t>102; 112; 122; 143; 231; 241; 251; 272; 360; 370; 380; 401; 489; 499; 509; 530; 618</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -12872,7 +13871,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'gpu_op_uid': 2485, 'count': 17, 'total_duration_us': np.float64(85.736), 'gpu_op_uids': [2485, 2487, 2489, 2493, 2509, 2511, 2513, 2517, 2533, 2535, 2537, 2541, 2557, 2559, 2561, 2565, 2581], 'mean_duration_us': np.float64(5.043294117647059), 'median_duration_us': np.float64(5.01), 'std_dev_duration_us': np.float64(0.2192558979569931), 'min_duration_us': np.float64(4.729), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 17, 'total_duration_us': np.float64(85.736), 'gpu_op_uids': [2485, 2487, 2489, 2493, 2509, 2511, 2513, 2517, 2533, 2535, 2537, 2541, 2557, 2559, 2561, 2565, 2581], 'mean_duration_us': np.float64(5.043294117647059), 'median_duration_us': np.float64(5.01), 'std_dev_duration_us': np.float64(0.2192558979569931), 'min_duration_us': np.float64(4.729), 'max_duration_us': np.float64(5.491)}]</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -12888,10 +13887,15 @@
       <c r="BC3" t="b">
         <v>1</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
         <v>21.94156098133965</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BF3" t="n">
         <v>51.02823731994756</v>
       </c>
     </row>
@@ -13007,7 +14011,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>31; 100; 129; 180; 209; 260; 289; 340; 369; 386</t>
+          <t>61; 159; 212; 288; 341; 417; 470; 546; 599; 638</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -13077,7 +14081,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 2477, 'count': 10, 'total_duration_us': np.float64(39.519000000000005), 'gpu_op_uids': [2477, 2497, 2507, 2521, 2531, 2545, 2555, 2569, 2579, 2585], 'mean_duration_us': np.float64(3.9519000000000006), 'median_duration_us': np.float64(3.948), 'std_dev_duration_us': np.float64(0.17117561158062206), 'min_duration_us': np.float64(3.728), 'max_duration_us': np.float64(4.209)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(39.519000000000005), 'gpu_op_uids': [2477, 2497, 2507, 2521, 2531, 2545, 2555, 2569, 2579, 2585], 'mean_duration_us': np.float64(3.9519000000000006), 'median_duration_us': np.float64(3.948), 'std_dev_duration_us': np.float64(0.17117561158062206), 'min_duration_us': np.float64(3.728), 'max_duration_us': np.float64(4.209)}]</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -13093,10 +14097,15 @@
       <c r="BC4" t="b">
         <v>1</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>aten::layer_norm =&gt; aten::layer_norm =&gt; torch/nn/functional.py(2889): layer_norm =&gt; torch/nn/modules/normalization.py(216): forward</t>
+        </is>
+      </c>
+      <c r="BE4" t="n">
         <v>10.11367654979113</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BF4" t="n">
         <v>61.14191386973869</v>
       </c>
     </row>
@@ -13212,7 +14221,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>106; 186; 266; 346</t>
+          <t>174; 303; 432; 561</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -13282,7 +14291,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT32x64x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'gpu_op_uid': 2499, 'count': 4, 'total_duration_us': np.float64(33.794), 'gpu_op_uids': [2499, 2523, 2547, 2571], 'mean_duration_us': np.float64(8.4485), 'median_duration_us': np.float64(7.276), 'std_dev_duration_us': np.float64(2.1389002431156063), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(12.147)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT32x64x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(33.794), 'gpu_op_uids': [2499, 2523, 2547, 2571], 'mean_duration_us': np.float64(8.4485), 'median_duration_us': np.float64(7.276), 'std_dev_duration_us': np.float64(2.1389002431156063), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(12.147)}]</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -13298,10 +14307,15 @@
       <c r="BC5" t="b">
         <v>1</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
         <v>8.648639867641858</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
         <v>69.79055373738055</v>
       </c>
     </row>
@@ -13417,7 +14431,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>117; 197; 277; 357</t>
+          <t>196; 325; 454; 583</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -13487,7 +14501,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'gpu_op_uid': 2503, 'count': 4, 'total_duration_us': np.float64(29.063000000000002), 'gpu_op_uids': [2503, 2527, 2551, 2575], 'mean_duration_us': np.float64(7.265750000000001), 'median_duration_us': np.float64(7.296), 'std_dev_duration_us': np.float64(0.10763450887145837), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(7.376)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(29.063000000000002), 'gpu_op_uids': [2503, 2527, 2551, 2575], 'mean_duration_us': np.float64(7.265750000000001), 'median_duration_us': np.float64(7.296), 'std_dev_duration_us': np.float64(0.10763450887145837), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(7.376)}]</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -13503,10 +14517,15 @@
       <c r="BC6" t="b">
         <v>1</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward</t>
+        </is>
+      </c>
+      <c r="BE6" t="n">
         <v>7.437772804350624</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>77.22832654173118</v>
       </c>
     </row>
@@ -13614,7 +14633,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>648</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -13682,7 +14701,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x144x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 2587, 'count': 1, 'total_duration_us': np.float64(25.537), 'gpu_op_uids': [2587], 'mean_duration_us': np.float64(25.537), 'median_duration_us': np.float64(25.537), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(25.537), 'max_duration_us': np.float64(25.537)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x144x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(25.537), 'gpu_op_uids': [2587], 'mean_duration_us': np.float64(25.537), 'median_duration_us': np.float64(25.537), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(25.537), 'max_duration_us': np.float64(25.537)}]</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -13698,10 +14717,15 @@
       <c r="BC7" t="b">
         <v>1</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>aten::addmm =&gt; aten::addmm =&gt; aten::linear =&gt; torch/nn/modules/linear.py(124): forward</t>
+        </is>
+      </c>
+      <c r="BE7" t="n">
         <v>6.535433169260221</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BF7" t="n">
         <v>83.76375971099139</v>
       </c>
     </row>
@@ -13817,7 +14841,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14; 94; 123; 174; 203; 254; 283; 334; 363</t>
+          <t>34; 148; 201; 277; 330; 406; 459; 535; 588</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -13887,7 +14911,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 2471, 'count': 9, 'total_duration_us': np.float64(19.315), 'gpu_op_uids': [2471, 2495, 2505, 2519, 2529, 2543, 2553, 2567, 2577], 'mean_duration_us': np.float64(2.1461111111111113), 'median_duration_us': np.float64(2.124), 'std_dev_duration_us': np.float64(0.12095953817927378), 'min_duration_us': np.float64(1.964), 'max_duration_us': np.float64(2.324)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(19.315), 'gpu_op_uids': [2471, 2495, 2505, 2519, 2529, 2543, 2553, 2567, 2577], 'mean_duration_us': np.float64(2.1461111111111113), 'median_duration_us': np.float64(2.124), 'std_dev_duration_us': np.float64(0.12095953817927378), 'min_duration_us': np.float64(1.964), 'max_duration_us': np.float64(2.324)}]</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -13903,10 +14927,15 @@
       <c r="BC8" t="b">
         <v>1</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>aten::add =&gt; aten::add =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl</t>
+        </is>
+      </c>
+      <c r="BE8" t="n">
         <v>4.943186717200685</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BF8" t="n">
         <v>88.70694642819208</v>
       </c>
     </row>
@@ -14000,7 +15029,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>111; 191; 271; 351</t>
+          <t>183; 312; 441; 570</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -14046,7 +15075,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 2501, 'count': 4, 'total_duration_us': np.float64(18.638), 'gpu_op_uids': [2501, 2525, 2549, 2573], 'mean_duration_us': np.float64(4.6595), 'median_duration_us': np.float64(4.83), 'std_dev_duration_us': np.float64(0.5681467680098163), 'min_duration_us': np.float64(3.768), 'max_duration_us': np.float64(5.21)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(18.638), 'gpu_op_uids': [2501, 2525, 2549, 2573], 'mean_duration_us': np.float64(4.6595), 'median_duration_us': np.float64(4.83), 'std_dev_duration_us': np.float64(0.5681467680098163), 'min_duration_us': np.float64(3.768), 'max_duration_us': np.float64(5.21)}]</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -14058,10 +15087,15 @@
       <c r="BC9" t="b">
         <v>0</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>aten::gelu =&gt; aten::gelu =&gt; transformers/activations.py(77): forward =&gt; torch/nn/modules/module.py(1755): _call_impl</t>
+        </is>
+      </c>
+      <c r="BE9" t="n">
         <v>4.769741569228731</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BF9" t="n">
         <v>93.47668799742081</v>
       </c>
     </row>
@@ -14151,7 +15185,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -14197,7 +15231,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt;)', 'stream': 0, 'gpu_op_uid': 2481, 'count': 1, 'total_duration_us': np.float64(4.329), 'gpu_op_uids': [2481], 'mean_duration_us': np.float64(4.329), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(4.329)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.329), 'gpu_op_uids': [2481], 'mean_duration_us': np.float64(4.329), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(4.329)}]</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -14209,10 +15243,15 @@
       <c r="BC10" t="b">
         <v>0</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>aten::all =&gt; aten::all =&gt; transformers/modeling_attn_mask_utils.py(429): _prepared_attention_mask_for_sdpa =&gt; transformers/models/bert/modeling_bert.py(1001): forward</t>
+        </is>
+      </c>
+      <c r="BE10" t="n">
         <v>1.107899626743043</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
         <v>94.58458762416386</v>
       </c>
     </row>
@@ -14302,7 +15341,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -14348,7 +15387,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 2479, 'count': 1, 'total_duration_us': np.float64(4.048), 'gpu_op_uids': [2479], 'mean_duration_us': np.float64(4.048), 'median_duration_us': np.float64(4.048), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(4.048)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.048), 'gpu_op_uids': [2479], 'mean_duration_us': np.float64(4.048), 'median_duration_us': np.float64(4.048), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(4.048)}]</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -14360,10 +15399,15 @@
       <c r="BC11" t="b">
         <v>0</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>aten::eq =&gt; aten::eq =&gt; transformers/modeling_attn_mask_utils.py(429): _prepared_attention_mask_for_sdpa =&gt; transformers/models/bert/modeling_bert.py(1001): forward</t>
+        </is>
+      </c>
+      <c r="BE11" t="n">
         <v>1.035922389544307</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BF11" t="n">
         <v>95.62051001370817</v>
       </c>
     </row>
@@ -14453,7 +15497,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -14499,7 +15543,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'gpu_op_uid': 2473, 'count': 1, 'total_duration_us': np.float64(3.327), 'gpu_op_uids': [2473], 'mean_duration_us': np.float64(3.327), 'median_duration_us': np.float64(3.327), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.327), 'max_duration_us': np.float64(3.327)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(3.327), 'gpu_op_uids': [2473], 'mean_duration_us': np.float64(3.327), 'median_duration_us': np.float64(3.327), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.327), 'max_duration_us': np.float64(3.327)}]</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -14511,10 +15555,15 @@
       <c r="BC12" t="b">
         <v>0</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>aten::index_select =&gt; aten::index_select =&gt; aten::embedding =&gt; torch/nn/functional.py(2437): embedding</t>
+        </is>
+      </c>
+      <c r="BE12" t="n">
         <v>0.8514807192225459</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BF12" t="n">
         <v>96.47199073293072</v>
       </c>
     </row>
@@ -14604,7 +15653,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -14650,7 +15699,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'gpu_op_uid': 2467, 'count': 1, 'total_duration_us': np.float64(3.086), 'gpu_op_uids': [2467], 'mean_duration_us': np.float64(3.086), 'median_duration_us': np.float64(3.086), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.086), 'max_duration_us': np.float64(3.086)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(3.086), 'gpu_op_uids': [2467], 'mean_duration_us': np.float64(3.086), 'median_duration_us': np.float64(3.086), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.086), 'max_duration_us': np.float64(3.086)}]</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -14662,10 +15711,15 @@
       <c r="BC13" t="b">
         <v>0</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>aten::index_select =&gt; aten::index_select =&gt; aten::embedding =&gt; torch/nn/functional.py(2437): embedding</t>
+        </is>
+      </c>
+      <c r="BE13" t="n">
         <v>0.78975024148613</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>97.26174097441685</v>
       </c>
     </row>
@@ -14755,7 +15809,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>627</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -14801,7 +15855,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 2583, 'count': 1, 'total_duration_us': np.float64(3.086), 'gpu_op_uids': [2583], 'mean_duration_us': np.float64(3.086), 'median_duration_us': np.float64(3.086), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.086), 'max_duration_us': np.float64(3.086)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(3.086), 'gpu_op_uids': [2583], 'mean_duration_us': np.float64(3.086), 'median_duration_us': np.float64(3.086), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.086), 'max_duration_us': np.float64(3.086)}]</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -14813,10 +15867,15 @@
       <c r="BC14" t="b">
         <v>0</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>aten::gelu =&gt; aten::gelu =&gt; transformers/activations.py(77): forward =&gt; torch/nn/modules/module.py(1755): _call_impl</t>
+        </is>
+      </c>
+      <c r="BE14" t="n">
         <v>0.78975024148613</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BF14" t="n">
         <v>98.05149121590298</v>
       </c>
     </row>
@@ -14906,7 +15965,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -14952,7 +16011,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'gpu_op_uid': 2469, 'count': 1, 'total_duration_us': np.float64(2.645), 'gpu_op_uids': [2469], 'mean_duration_us': np.float64(2.645), 'median_duration_us': np.float64(2.645), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.645), 'max_duration_us': np.float64(2.645)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.645), 'gpu_op_uids': [2469], 'mean_duration_us': np.float64(2.645), 'median_duration_us': np.float64(2.645), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.645), 'max_duration_us': np.float64(2.645)}]</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -14964,10 +16023,15 @@
       <c r="BC15" t="b">
         <v>0</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>aten::index_select =&gt; aten::index_select =&gt; aten::embedding =&gt; torch/nn/functional.py(2437): embedding</t>
+        </is>
+      </c>
+      <c r="BE15" t="n">
         <v>0.6769109269193617</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BF15" t="n">
         <v>98.72840214282235</v>
       </c>
     </row>
@@ -15075,7 +16139,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -15143,7 +16207,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 2475, 'count': 1, 'total_duration_us': np.float64(2.565), 'gpu_op_uids': [2475], 'mean_duration_us': np.float64(2.565), 'median_duration_us': np.float64(2.565), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.565), 'max_duration_us': np.float64(2.565)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.565), 'gpu_op_uids': [2475], 'mean_duration_us': np.float64(2.565), 'median_duration_us': np.float64(2.565), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.565), 'max_duration_us': np.float64(2.565)}]</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -15159,10 +16223,15 @@
       <c r="BC16" t="b">
         <v>1</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>aten::add_ =&gt; aten::add_ =&gt; transformers/models/bert/modeling_bert.py(181): forward =&gt; torch/nn/modules/module.py(1755): _call_impl</t>
+        </is>
+      </c>
+      <c r="BE16" t="n">
         <v>0.6564174079947217</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BF16" t="n">
         <v>99.38481955081707</v>
       </c>
     </row>
@@ -15252,7 +16321,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -15298,7 +16367,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'gpu_op_uid': 2483, 'count': 1, 'total_duration_us': np.float64(2.404), 'gpu_op_uids': [2483], 'mean_duration_us': np.float64(2.404), 'median_duration_us': np.float64(2.404), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.404), 'max_duration_us': np.float64(2.404)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.404), 'gpu_op_uids': [2483], 'mean_duration_us': np.float64(2.404), 'median_duration_us': np.float64(2.404), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.404), 'max_duration_us': np.float64(2.404)}]</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -15310,1036 +16379,16 @@
       <c r="BC17" t="b">
         <v>0</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>aten::_local_scalar_dense =&gt; aten::_local_scalar_dense =&gt; aten::item =&gt; aten::is_nonzero</t>
+        </is>
+      </c>
+      <c r="BE17" t="n">
         <v>0.6151804491829459</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BF17" t="n">
         <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AW5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>param: M</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>param: N</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>param: K</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>param: bias</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>param: stride_A</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>param: stride_B</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>param: dtype_A_B</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>param: B</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>param: transpose</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>num_kernels</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>GFLOPS_first</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Data Moved (MB)_first</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>FLOPS/Byte_first</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_mean</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_median</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_std</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_min</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_max</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_mean</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_median</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_std</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_max</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>process_name_first</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>process_label_first</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>thread_name_first</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Compute Spec</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Time (µs)_first</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Bound_first</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_mean</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_median</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_std</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_min</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_max</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details__summarize_kernel_stats</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>trunc_kernel_details</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims_first</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Input type_first</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides_first</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs_first</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>UID_first</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>aten::addmm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(512, 1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(1, 512)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>(True, False)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0739968</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7763671875</v>
-      </c>
-      <c r="N2" t="n">
-        <v>90.89622641509433</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.161716610441385</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.162498619883041</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.007093321468841064</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.1482514529610528</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1721461889519876</v>
-      </c>
-      <c r="T2" t="n">
-        <v>14.69942963776174</v>
-      </c>
-      <c r="U2" t="n">
-        <v>14.77051134502924</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.6447561542668266</v>
-      </c>
-      <c r="W2" t="n">
-        <v>13.47549763471456</v>
-      </c>
-      <c r="X2" t="n">
-        <v>15.64743896747548</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.1536</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>3.051256800780849</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3.066011695906433</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.1338362541290766</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.797197225680242</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.248041300980898</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'gpu_op_uid': 2485, 'count': 17, 'total_duration_us': np.float64(85.736), 'gpu_op_uids': [2485, 2487, 2489, 2493, 2509, 2511, 2513, 2517, 2533, 2535, 2537, 2541, 2557, 2559, 2561, 2565, 2581], 'mean_duration_us': np.float64(5.043294117647059), 'median_duration_us': np.float64(5.01), 'std_dev_duration_us': np.float64(0.2192558979569931), 'min_duration_us': np.float64(4.729), 'max_duration_us': np.float64(5.491)}]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(5.04)}]</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>[[512], [141, 512], [512, 512], [], []]</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>[[1], [512, 1], [1, 512], [], []]</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.043313419117647</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.009765625</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.2260085446570848</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.72900390625</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.4912109375</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>85.736328125</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>aten::addmm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(512, 1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>(1, 512)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>(True, False)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.2959872</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.6923828125</v>
-      </c>
-      <c r="N3" t="n">
-        <v>104.8422198041349</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.3516526762042594</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.3881479117816242</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.07985573206817134</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.2324174162479399</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3978974650058495</v>
-      </c>
-      <c r="T3" t="n">
-        <v>36.86804717331926</v>
-      </c>
-      <c r="U3" t="n">
-        <v>40.69428868352502</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8.372252214111324</v>
-      </c>
-      <c r="W3" t="n">
-        <v>24.36715784057563</v>
-      </c>
-      <c r="X3" t="n">
-        <v>41.71645348565136</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.5326732075471698</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>6.634956154797349</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>7.323545505313666</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.506711925814554</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>4.385234268829055</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>7.507499339733011</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT32x64x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'gpu_op_uid': 2499, 'count': 4, 'total_duration_us': np.float64(33.794), 'gpu_op_uids': [2499, 2523, 2547, 2571], 'mean_duration_us': np.float64(8.4485), 'median_duration_us': np.float64(7.276), 'std_dev_duration_us': np.float64(2.1389002431156063), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(12.147)}]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT32x64x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(8.45)}]</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>[[2048], [141, 512], [512, 2048], [], []]</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>[[1], [512, 1], [1, 512], [], []]</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AP3" t="n">
-        <v>8.4486083984375</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.276123046875</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.469693365812908</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.09521484375</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12.14697265625</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>33.79443359375</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>aten::addmm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(2048, 1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>(1, 2048)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>(True, False)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.295770624</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.689453125</v>
-      </c>
-      <c r="N4" t="n">
-        <v>104.8796296296296</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.3882216110630076</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.3865433379125297</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.006701070029764123</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.3823352712829339</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3974644971440369</v>
-      </c>
-      <c r="T4" t="n">
-        <v>40.71653878250636</v>
-      </c>
-      <c r="U4" t="n">
-        <v>40.5405221160669</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.7028057428438708</v>
-      </c>
-      <c r="W4" t="n">
-        <v>40.09918164649808</v>
-      </c>
-      <c r="X4" t="n">
-        <v>41.68592925139357</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.5320935849056604</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>7.324936057792596</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.293270526651504</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.1264352835804546</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>7.213873043074226</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7.499330134793149</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'gpu_op_uid': 2503, 'count': 4, 'total_duration_us': np.float64(29.063000000000002), 'gpu_op_uids': [2503, 2527, 2551, 2575], 'mean_duration_us': np.float64(7.265750000000001), 'median_duration_us': np.float64(7.296), 'std_dev_duration_us': np.float64(0.10763450887145837), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(7.376)}]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(7.27)}]</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>[[512], [141, 2048], [2048, 512], [], []]</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>[[1], [2048, 1], [1, 2048], [], []]</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.2657470703125</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.2958984375</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.1241722515736194</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.09521484375</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.3759765625</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>29.06298828125</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>aten::addmm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>30522</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(512, 1)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>(1, 512)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>(True, False)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>4.41119205</v>
-      </c>
-      <c r="M5" t="n">
-        <v>38.21102142333984</v>
-      </c>
-      <c r="N5" t="n">
-        <v>110.0949518258843</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.568977890630975</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.568977890630975</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>1.568977890630975</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.568977890630975</v>
-      </c>
-      <c r="T5" t="n">
-        <v>172.7365452848948</v>
-      </c>
-      <c r="U5" t="n">
-        <v>172.7365452848948</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>172.7365452848948</v>
-      </c>
-      <c r="X5" t="n">
-        <v>172.7365452848948</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.559841509433963</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>29.60335642699953</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>29.60335642699953</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>29.60335642699953</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>29.60335642699953</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x144x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 2587, 'count': 1, 'total_duration_us': np.float64(25.537), 'gpu_op_uids': [2587], 'mean_duration_us': np.float64(25.537), 'median_duration_us': np.float64(25.537), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(25.537), 'max_duration_us': np.float64(25.537)}]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x144x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(25.54)}]</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>[[30522], [141, 512], [512, 30522], [], []]</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>[[1], [512, 1], [1, 512], [], []]</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AP5" t="n">
-        <v>25.537109375</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>25.537109375</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>25.537109375</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>25.537109375</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>25.537109375</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -16353,7 +16402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16364,250 +16413,240 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>param: M</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: N</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: K</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: bias</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_A_B</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>param: B</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>param: N_Q</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>param: H_Q</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>param: N_KV</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>param: H_KV</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>param: d_h_qk</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>param: d_h_v</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>param: dropout</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>param: causal</t>
+          <t>param: transpose</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>param: flash_impl</t>
+          <t>num_kernels</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_A_B</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>num_kernels</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>process_name_first</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>process_label_first</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>thread_name_first</t>
+          <t>Roofline Time (µs)_first</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Compute Spec</t>
+          <t>Roofline Bound_first</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Roofline Time (µs)_first</t>
+          <t>Pct Roofline_mean</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Roofline Bound_first</t>
+          <t>Pct Roofline_median</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_mean</t>
+          <t>Pct Roofline_std</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_median</t>
+          <t>Pct Roofline_min</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_std</t>
+          <t>Pct Roofline_max</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_min</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_max</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -16616,204 +16655,765 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::_scaled_dot_product_flash_attention</t>
+          <t>aten::addmm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(512, 1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(1, 512)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(True, False)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0739968</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7763671875</v>
+      </c>
+      <c r="N2" t="n">
+        <v>90.89622641509433</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.161716610441385</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.162498619883041</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.007093321468841064</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1482514529610528</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1721461889519876</v>
+      </c>
+      <c r="T2" t="n">
+        <v>14.69942963776174</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14.77051134502924</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6447561542668266</v>
+      </c>
+      <c r="W2" t="n">
+        <v>13.47549763471456</v>
+      </c>
+      <c r="X2" t="n">
+        <v>15.64743896747548</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>thread 6240 (python3)</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>MEMORY_BOUND</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.051256800780849</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.066011695906433</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.1338362541290766</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.797197225680242</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.248041300980898</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 17, 'total_duration_us': np.float64(85.736), 'gpu_op_uids': [2485, 2487, 2489, 2493, 2509, 2511, 2513, 2517, 2533, 2535, 2537, 2541, 2557, 2559, 2561, 2565, 2581], 'mean_duration_us': np.float64(5.043294117647059), 'median_duration_us': np.float64(5.01), 'std_dev_duration_us': np.float64(0.2192558979569931), 'min_duration_us': np.float64(4.729), 'max_duration_us': np.float64(5.491)}]</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(5.04)}]</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>[[512], [141, 512], [512, 512], [], []]</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>[[1], [512, 1], [1, 512], [], []]</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.043313419117647</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.009765625</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.2260085446570848</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.72900390625</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.4912109375</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>85.736328125</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(512, 1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>(1, 512)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>(True, False)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2959872</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.6923828125</v>
+      </c>
+      <c r="N3" t="n">
+        <v>104.8422198041349</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3516526762042594</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3881479117816242</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.07985573206817134</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2324174162479399</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3978974650058495</v>
+      </c>
+      <c r="T3" t="n">
+        <v>36.86804717331926</v>
+      </c>
+      <c r="U3" t="n">
+        <v>40.69428868352502</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.372252214111324</v>
+      </c>
+      <c r="W3" t="n">
+        <v>24.36715784057563</v>
+      </c>
+      <c r="X3" t="n">
+        <v>41.71645348565136</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>thread 6240 (python3)</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5326732075471698</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>MEMORY_BOUND</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>6.634956154797349</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>7.323545505313666</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.506711925814554</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>4.385234268829055</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.507499339733011</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT32x64x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(33.794), 'gpu_op_uids': [2499, 2523, 2547, 2571], 'mean_duration_us': np.float64(8.4485), 'median_duration_us': np.float64(7.276), 'std_dev_duration_us': np.float64(2.1389002431156063), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(12.147)}]</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT32x64x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(8.45)}]</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>[[2048], [141, 512], [512, 2048], [], []]</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>[[1], [512, 1], [1, 512], [], []]</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.4486083984375</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.276123046875</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.469693365812908</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.09521484375</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12.14697265625</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>33.79443359375</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(2048, 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>(1, 2048)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0.040716288</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.55078125</v>
-      </c>
-      <c r="P2" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.02042813609383138</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.02113869129033006</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.001603842596794618</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.01802984250480168</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.02140531928986373</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.440183594615113</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.49027773596827</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.1130709030740206</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.271103896588519</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.509075009935393</v>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>(True, False)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.295770624</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.689453125</v>
+      </c>
+      <c r="N4" t="n">
+        <v>104.8796296296296</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3882216110630076</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3865433379125297</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.006701070029764123</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3823352712829339</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3974644971440369</v>
+      </c>
+      <c r="T4" t="n">
+        <v>40.71653878250636</v>
+      </c>
+      <c r="U4" t="n">
+        <v>40.5405221160669</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7028057428438708</v>
+      </c>
+      <c r="W4" t="n">
+        <v>40.09918164649808</v>
+      </c>
+      <c r="X4" t="n">
+        <v>41.68592925139357</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>thread 6240 (python3)</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>0.1089690566037736</v>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AC4" t="n">
+        <v>0.5320935849056604</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>MEMORY_BOUND</t>
         </is>
       </c>
-      <c r="AG2" t="n">
-        <v>0.3854365300722902</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.3988432318930201</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.03026118107159661</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.3401857076377676</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.4038739488653533</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>[{'name': 'attn_fwd', 'stream': 0, 'gpu_op_uid': 2491, 'count': 4, 'total_duration_us': np.float64(113.656), 'gpu_op_uids': [2491, 2515, 2539, 2563], 'mean_duration_us': np.float64(28.414), 'median_duration_us': np.float64(27.3215), 'std_dev_duration_us': np.float64(2.0935189275475854), 'min_duration_us': np.float64(26.981), 'max_duration_us': np.float64(32.032)}]</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>[{'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(28.41)}]</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>[[1, 8, 141, 64], [1, 8, 141, 64], [1, 8, 141, 64], [], [], [], []]</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>[[72192, 64, 512, 1], [72192, 64, 512, 1], [72192, 64, 512, 1], [], [], [], []]</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>['', '', '', '0.', 'False', 'False', '0.125']</t>
-        </is>
-      </c>
-      <c r="AR2" t="n">
-        <v>28.4139404296875</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>27.3212890625</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.417572675156308</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>26.98095703125</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>32.0322265625</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>113.65576171875</v>
-      </c>
-      <c r="AX2" t="n">
+      <c r="AE4" t="n">
+        <v>7.324936057792596</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7.293270526651504</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1264352835804546</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7.213873043074226</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.499330134793149</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(29.063000000000002), 'gpu_op_uids': [2503, 2527, 2551, 2575], 'mean_duration_us': np.float64(7.265750000000001), 'median_duration_us': np.float64(7.296), 'std_dev_duration_us': np.float64(0.10763450887145837), 'min_duration_us': np.float64(7.095), 'max_duration_us': np.float64(7.376)}]</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(7.27)}]</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>[[512], [141, 2048], [2048, 512], [], []]</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>[[1], [2048, 1], [1, 2048], [], []]</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.2657470703125</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.2958984375</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1241722515736194</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.09521484375</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.3759765625</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>29.06298828125</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4</v>
       </c>
-      <c r="AY2" t="n">
-        <v>79</v>
+      <c r="AW4" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30522</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(512, 1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>(1, 512)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>(True, False)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>4.41119205</v>
+      </c>
+      <c r="M5" t="n">
+        <v>38.21102142333984</v>
+      </c>
+      <c r="N5" t="n">
+        <v>110.0949518258843</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.568977890630975</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.568977890630975</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1.568977890630975</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.568977890630975</v>
+      </c>
+      <c r="T5" t="n">
+        <v>172.7365452848948</v>
+      </c>
+      <c r="U5" t="n">
+        <v>172.7365452848948</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>172.7365452848948</v>
+      </c>
+      <c r="X5" t="n">
+        <v>172.7365452848948</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>thread 6240 (python3)</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.559841509433963</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>MEMORY_BOUND</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>29.60335642699953</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>29.60335642699953</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>29.60335642699953</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>29.60335642699953</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x144x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(25.537), 'gpu_op_uids': [2587], 'mean_duration_us': np.float64(25.537), 'median_duration_us': np.float64(25.537), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(25.537), 'max_duration_us': np.float64(25.537)}]</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x144x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(25.54)}]</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>[[30522], [141, 512], [512, 30522], [], []]</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>[[1], [512, 1], [1, 512], [], []]</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>25.537109375</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>25.537109375</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>25.537109375</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>25.537109375</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>25.537109375</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -16827,7 +17427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16838,225 +17438,250 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>param: shape_in1</t>
+          <t>param: B</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>param: shape_in2</t>
+          <t>param: N_Q</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_in1_in2_out</t>
+          <t>param: H_Q</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input1</t>
+          <t>param: N_KV</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input2</t>
+          <t>param: H_KV</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>param: d_h_qk</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>param: d_h_v</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>param: dropout</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>param: causal</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>param: flash_impl</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_A_B</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>num_kernels</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Roofline Time (µs)_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Roofline Bound_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_mean</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_median</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_std</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_min</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_max</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -17065,349 +17690,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::_scaled_dot_product_flash_attention</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(1, 141, 512)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(1, 141, 512)</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(72192, 512, 1)</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(72192, 512, 1)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>7.2192e-05</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.4130859375</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.2024691163681418</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.2039299531034483</v>
-      </c>
       <c r="N2" t="n">
-        <v>0.01209316084881078</v>
+        <v>0.040716288</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1863645579831933</v>
+        <v>0.55078125</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2205607399303829</v>
+        <v>70.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03374485272802363</v>
+        <v>0.02042813609383138</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03398832551724138</v>
+        <v>0.02113869129033006</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00201552680813513</v>
+        <v>0.001603842596794618</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03106075966386555</v>
+        <v>0.01802984250480168</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03676012332173048</v>
-      </c>
-      <c r="V2" t="inlineStr">
+        <v>0.02140531928986373</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.440183594615113</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.49027773596827</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.1130709030740206</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.271103896588519</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.509075009935393</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>thread 6240 (python3)</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0817267924528302</v>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1089690566037736</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>MEMORY_BOUND</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>3.820172006946072</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.847734964216006</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.2281728462039772</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3.516312414777232</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4.161523394912885</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 2471, 'count': 9, 'total_duration_us': np.float64(19.315), 'gpu_op_uids': [2471, 2495, 2505, 2519, 2529, 2543, 2553, 2567, 2577], 'mean_duration_us': np.float64(2.1461111111111113), 'median_duration_us': np.float64(2.124), 'std_dev_duration_us': np.float64(0.12095953817927378), 'min_duration_us': np.float64(1.964), 'max_duration_us': np.float64(2.324)}]</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(2.15)}]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[[1, 141, 512], [1, 141, 512], []]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[[72192, 512, 1], [72192, 512, 1], []]</t>
-        </is>
+      <c r="AG2" t="n">
+        <v>0.3854365300722902</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3988432318930201</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.03026118107159661</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3401857076377676</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.4038739488653533</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>['', '', '1']</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>2.146158854166667</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.1240234375</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.1284207535938537</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.9638671875</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.32421875</v>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(113.656), 'gpu_op_uids': [2491, 2515, 2539, 2563], 'mean_duration_us': np.float64(28.414), 'median_duration_us': np.float64(27.3215), 'std_dev_duration_us': np.float64(2.0935189275475854), 'min_duration_us': np.float64(26.981), 'max_duration_us': np.float64(32.032)}]</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(28.41)}]</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>[[1, 8, 141, 64], [1, 8, 141, 64], [1, 8, 141, 64], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>[[72192, 64, 512, 1], [72192, 64, 512, 1], [72192, 64, 512, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>['', '', '', '0.', 'False', 'False', '0.125']</t>
+        </is>
       </c>
       <c r="AR2" t="n">
-        <v>19.3154296875</v>
+        <v>28.4139404296875</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>27.3212890625</v>
       </c>
       <c r="AT2" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>aten::add_</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>(1, 141, 512)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(1, 141, 512)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(72192, 512, 1)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(72192, 512, 1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>7.2192e-05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.4130859375</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.1688740331239292</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.1688740331239292</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0.1688740331239292</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.1688740331239292</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.02814567218732153</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.02814567218732153</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>0.02814567218732153</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.02814567218732153</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0817267924528302</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.186302511772249</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.186302511772249</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>3.186302511772249</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3.186302511772249</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 2475, 'count': 1, 'total_duration_us': np.float64(2.565), 'gpu_op_uids': [2475], 'mean_duration_us': np.float64(2.565), 'median_duration_us': np.float64(2.565), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.565), 'max_duration_us': np.float64(2.565)}]</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(2.56)}]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[[1, 141, 512], [1, 141, 512], []]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[[72192, 512, 1], [72192, 512, 1], []]</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>2.56494140625</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.56494140625</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>2.56494140625</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2.56494140625</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.56494140625</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>27</v>
+        <v>2.417572675156308</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>26.98095703125</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>32.0322265625</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>113.65576171875</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -17421,7 +17901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV3"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17432,235 +17912,225 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>param: op_shape</t>
+          <t>param: shape_in1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_in_out</t>
+          <t>param: shape_in2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input</t>
+          <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>param: stride_input1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_input2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>param: num_channels</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>param: has_bias</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: is_affine</t>
+          <t>num_kernels</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>param: is_training</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>num_kernels</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>process_name_first</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>process_label_first</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>thread_name_first</t>
+          <t>Roofline Time (µs)_first</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Compute Spec</t>
+          <t>Roofline Bound_first</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Roofline Time (µs)_first</t>
+          <t>Pct Roofline_mean</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Roofline Bound_first</t>
+          <t>Pct Roofline_median</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_mean</t>
+          <t>Pct Roofline_std</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_median</t>
+          <t>Pct Roofline_min</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_std</t>
+          <t>Pct Roofline_max</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_min</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Pct Roofline_max</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -17669,7 +18139,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::layer_norm</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17679,185 +18149,175 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', None)</t>
+          <t>(1, 141, 512)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>(72192, 512, 1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(72192, 512, 1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="I2" t="n">
+        <v>7.2192e-05</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4130859375</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.000364032</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.28125</v>
+        <v>0.2024691163681418</v>
       </c>
       <c r="M2" t="n">
-        <v>1.234375</v>
+        <v>0.2039299531034483</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07476479069970718</v>
+        <v>0.01209316084881078</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07470099932966896</v>
+        <v>0.1863645579831933</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003397537390332268</v>
+        <v>0.2205607399303829</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.07006725939675175</v>
+        <v>0.03374485272802363</v>
       </c>
       <c r="R2" t="n">
-        <v>0.07910671591355599</v>
+        <v>0.03398832551724138</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09228778851995104</v>
+        <v>0.00201552680813513</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09220904604756011</v>
+        <v>0.03106075966386555</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004193835216191402</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.08648927331786543</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.09764735245579566</v>
+        <v>0.03676012332173048</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 6240 (python3)</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0817267924528302</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>MEMORY_BOUND</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.05564377358490566</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
+        <v>3.820172006946072</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.847734964216006</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.410656428296362</v>
+        <v>0.2281728462039772</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.409452817540924</v>
+        <v>3.516312414777232</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.06410447906287296</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.322023762202863</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.492579545538792</v>
+        <v>4.161523394912885</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(19.315), 'gpu_op_uids': [2471, 2495, 2505, 2519, 2529, 2543, 2553, 2567, 2577], 'mean_duration_us': np.float64(2.1461111111111113), 'median_duration_us': np.float64(2.124), 'std_dev_duration_us': np.float64(0.12095953817927378), 'min_duration_us': np.float64(1.964), 'max_duration_us': np.float64(2.324)}]</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(2.15)}]</t>
+        </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 2477, 'count': 10, 'total_duration_us': np.float64(39.519000000000005), 'gpu_op_uids': [2477, 2497, 2507, 2521, 2531, 2545, 2555, 2569, 2579, 2585], 'mean_duration_us': np.float64(3.9519000000000006), 'median_duration_us': np.float64(3.948), 'std_dev_duration_us': np.float64(0.17117561158062206), 'min_duration_us': np.float64(3.728), 'max_duration_us': np.float64(4.209)}]</t>
+          <t>[[1, 141, 512], [1, 141, 512], []]</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(3.95)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[[1, 141, 512], [], [512], [512], [], []]</t>
+          <t>[[72192, 512, 1], [72192, 512, 1], []]</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>[[72192, 512, 1], [], [1], [1], [], []]</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>['', '[512]', '', '', '9.9999999999999998e-13', 'True']</t>
-        </is>
+          <t>['', '', '1']</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>2.146158854166667</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.1240234375</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.951904296875</v>
+        <v>0.1284207535938537</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.947998046875</v>
+        <v>1.9638671875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1803733893005544</v>
+        <v>2.32421875</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.72802734375</v>
+        <v>19.3154296875</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.208984375</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>39.51904296875</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::native_layer_norm</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17867,179 +18327,161 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', None)</t>
+          <t>(1, 141, 512)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>(72192, 512, 1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(72192, 512, 1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="I3" t="n">
+        <v>7.2192e-05</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4130859375</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.000364032</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.28125</v>
+        <v>0.1688740331239292</v>
       </c>
       <c r="M3" t="n">
-        <v>1.234375</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.07476479069970718</v>
-      </c>
+        <v>0.1688740331239292</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0.07470099932966896</v>
+        <v>0.1688740331239292</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003397537390332268</v>
+        <v>0.1688740331239292</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07006725939675175</v>
+        <v>0.02814567218732153</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07910671591355599</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.09228778851995104</v>
-      </c>
+        <v>0.02814567218732153</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>0.09220904604756011</v>
+        <v>0.02814567218732153</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004193835216191402</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.08648927331786543</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.09764735245579566</v>
+        <v>0.02814567218732153</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 6240 (python3)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>thread 6240 (python3)</t>
-        </is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0817267924528302</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>MEMORY_BOUND</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.05564377358490566</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>MEMORY_BOUND</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.410656428296362</v>
-      </c>
+        <v>3.186302511772249</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.186302511772249</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>1.409452817540924</v>
+        <v>3.186302511772249</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06410447906287296</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.322023762202863</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.492579545538792</v>
+        <v>3.186302511772249</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.565), 'gpu_op_uids': [2475], 'mean_duration_us': np.float64(2.565), 'median_duration_us': np.float64(2.565), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.565), 'max_duration_us': np.float64(2.565)}]</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(2.56)}]</t>
+        </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 2477, 'count': 10, 'total_duration_us': np.float64(39.519000000000005), 'gpu_op_uids': [2477, 2497, 2507, 2521, 2531, 2545, 2555, 2569, 2579, 2585], 'mean_duration_us': np.float64(3.9519000000000006), 'median_duration_us': np.float64(3.948), 'std_dev_duration_us': np.float64(0.17117561158062206), 'min_duration_us': np.float64(3.728), 'max_duration_us': np.float64(4.209)}]</t>
+          <t>[[1, 141, 512], [1, 141, 512], []]</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(3.95)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>[[1, 141, 512], [], [512], [512], []]</t>
+          <t>[[72192, 512, 1], [72192, 512, 1], []]</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>[[72192, 512, 1], [], [1], [1], []]</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>['', '[512]', '', '', '9.9999999999999998e-13']</t>
-        </is>
-      </c>
-      <c r="AO3" t="n">
-        <v>3.951904296875</v>
-      </c>
+          <t>['', '', '1']</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>2.56494140625</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.56494140625</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>3.947998046875</v>
+        <v>2.56494140625</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.1803733893005544</v>
+        <v>2.56494140625</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.72802734375</v>
+        <v>2.56494140625</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.208984375</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
-        <v>39.51904296875</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
